--- a/data-raw/Variant Designation.xlsx
+++ b/data-raw/Variant Designation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="990" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="994" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t xml:space="preserve">phe_name</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">who_name</t>
   </si>
   <si>
+    <t xml:space="preserve">not_before_date</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unclassified</t>
   </si>
   <si>
@@ -194,14 +197,21 @@
   </si>
   <si>
     <t xml:space="preserve">Omicron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22JAN-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA.2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="YYYY\-MM\-DD"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -268,9 +278,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -290,20 +308,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="27.8061224489796"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="21.4642857142857"/>
-    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="19.7091836734694"/>
-    <col collapsed="false" hidden="false" max="5" min="4" style="0" width="37.7959183673469"/>
-    <col collapsed="false" hidden="false" max="6" min="6" style="0" width="13.5"/>
-    <col collapsed="false" hidden="false" max="7" min="7" style="0" width="37.7959183673469"/>
-    <col collapsed="false" hidden="false" max="8" min="8" style="0" width="30.780612244898"/>
-    <col collapsed="false" hidden="false" max="9" min="9" style="0" width="41.7142857142857"/>
-    <col collapsed="false" hidden="false" max="11" min="10" style="0" width="8.50510204081633"/>
-    <col collapsed="false" hidden="false" max="12" min="12" style="0" width="22.1377551020408"/>
-    <col collapsed="false" hidden="false" max="1025" min="13" style="0" width="8.50510204081633"/>
+    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="27.2704081632653"/>
+    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="20.7908163265306"/>
+    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="19.1683673469388"/>
+    <col collapsed="false" hidden="false" max="5" min="4" style="0" width="36.9897959183673"/>
+    <col collapsed="false" hidden="false" max="6" min="6" style="0" width="13.0918367346939"/>
+    <col collapsed="false" hidden="false" max="7" min="7" style="0" width="36.9897959183673"/>
+    <col collapsed="false" hidden="false" max="8" min="8" style="0" width="30.1020408163265"/>
+    <col collapsed="false" hidden="false" max="9" min="9" style="0" width="40.6326530612245"/>
+    <col collapsed="false" hidden="false" max="11" min="10" style="0" width="8.23469387755102"/>
+    <col collapsed="false" hidden="false" max="12" min="12" style="0" width="21.5969387755102"/>
+    <col collapsed="false" hidden="false" max="1025" min="13" style="0" width="8.23469387755102"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -316,246 +334,341 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>43831</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>4</v>
+      <c r="D3" s="1" t="n">
+        <v>43831</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>43831</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>43831</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>10</v>
+      <c r="D7" s="1" t="n">
+        <v>44112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>43927</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>18</v>
+      <c r="D11" s="1" t="n">
+        <v>43927</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44277</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44191</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44218</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44323</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44250</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44204</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44256</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44278</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44249</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>43937</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44501</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44531</v>
       </c>
     </row>
   </sheetData>
